--- a/data/tasques/02.20/ADG32/entregues/5796/02.20-5796-07_STOCK.xlsx
+++ b/data/tasques/02.20/ADG32/entregues/5796/02.20-5796-07_STOCK.xlsx
@@ -37,16 +37,16 @@
     <t>Saliente</t>
   </si>
   <si>
-    <t>[A0001] Cartutxo Tricolor/Negre HP 304 3JB05AE</t>
-  </si>
-  <si>
-    <t>[A0002] Cartutxo Bicolor/Negre Canon PG 575</t>
-  </si>
-  <si>
-    <t>[A0003] Kit Recarga Tinta Tricolor/Negre P4514</t>
-  </si>
-  <si>
-    <t>[A0004] Cartutxo Toner Negre Brother TN2410</t>
+    <t>[AP8461] Alcohol en gel desinfectant</t>
+  </si>
+  <si>
+    <t>[DF4598] Botiquí de primers auxilis compacte</t>
+  </si>
+  <si>
+    <t>[FA6235] Mascaretes quirúrgiques</t>
+  </si>
+  <si>
+    <t>[LA5365] Kit de protecció individual bàsic</t>
   </si>
 </sst>
 </file>
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="B2" s="3">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3">
         <v>0</v>
@@ -453,16 +453,16 @@
         <v>8</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3">
         <v>0</v>
@@ -476,16 +476,16 @@
         <v>9</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3">
         <v>0</v>
@@ -499,16 +499,16 @@
         <v>10</v>
       </c>
       <c r="B5" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3">
         <v>0</v>
